--- a/farmer_milk_data.xlsx
+++ b/farmer_milk_data.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AH$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AG$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="123">
   <si>
     <t>Farmer_Name</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Branch Code</t>
   </si>
   <si>
-    <t>Payment Duration</t>
-  </si>
-  <si>
     <t>Payment Status</t>
   </si>
   <si>
@@ -152,265 +149,256 @@
     <t>Cow</t>
   </si>
   <si>
+    <t>Paneer 200g</t>
+  </si>
+  <si>
+    <t>PNR200</t>
+  </si>
+  <si>
+    <t>Milk quality was good</t>
+  </si>
+  <si>
+    <t>SBIN000301</t>
+  </si>
+  <si>
+    <t>464546545440</t>
+  </si>
+  <si>
+    <t>REF184826</t>
+  </si>
+  <si>
+    <t>Saving</t>
+  </si>
+  <si>
+    <t>000301</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>290629</t>
+  </si>
+  <si>
+    <t>10092025F9012</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Ramesh Patel</t>
+  </si>
+  <si>
+    <t>F9013</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>Mix</t>
+  </si>
+  <si>
     <t>Skimmed Milk 500ml</t>
   </si>
   <si>
     <t>SKIM500</t>
   </si>
   <si>
-    <t>Milk quality was good</t>
-  </si>
-  <si>
-    <t>SBIN000301</t>
-  </si>
-  <si>
-    <t>464546545440</t>
+    <t>HDFC000145</t>
+  </si>
+  <si>
+    <t>502334112233</t>
+  </si>
+  <si>
+    <t>REF942636</t>
+  </si>
+  <si>
+    <t>001145</t>
+  </si>
+  <si>
+    <t>290630</t>
+  </si>
+  <si>
+    <t>10092025F9013</t>
+  </si>
+  <si>
+    <t>Kiran Desai</t>
+  </si>
+  <si>
+    <t>F9014</t>
+  </si>
+  <si>
+    <t>Nadiyad</t>
+  </si>
+  <si>
+    <t>Ghee 1L</t>
+  </si>
+  <si>
+    <t>GHEE1L</t>
+  </si>
+  <si>
+    <t>ICIC000287</t>
+  </si>
+  <si>
+    <t>721009988776</t>
+  </si>
+  <si>
+    <t>REF711630</t>
+  </si>
+  <si>
+    <t>002287</t>
+  </si>
+  <si>
+    <t>290631</t>
+  </si>
+  <si>
+    <t>10092025F9014</t>
+  </si>
+  <si>
+    <t>Amit Shah</t>
+  </si>
+  <si>
+    <t>F9015</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Buffalo</t>
+  </si>
+  <si>
+    <t>Curd 500g</t>
+  </si>
+  <si>
+    <t>CURD500</t>
+  </si>
+  <si>
+    <t>BOB000119</t>
+  </si>
+  <si>
+    <t>336699002211</t>
+  </si>
+  <si>
+    <t>REF254738</t>
+  </si>
+  <si>
+    <t>001119</t>
+  </si>
+  <si>
+    <t>290632</t>
+  </si>
+  <si>
+    <t>10092025F9015</t>
+  </si>
+  <si>
+    <t>REF704684</t>
+  </si>
+  <si>
+    <t>REF687808</t>
+  </si>
+  <si>
+    <t>REF526880</t>
+  </si>
+  <si>
+    <t>REF713190</t>
+  </si>
+  <si>
+    <t>REF228007</t>
+  </si>
+  <si>
+    <t>REF467823</t>
+  </si>
+  <si>
+    <t>REF511813</t>
+  </si>
+  <si>
+    <t>REF262971</t>
+  </si>
+  <si>
+    <t>REF741789</t>
+  </si>
+  <si>
+    <t>REF540642</t>
+  </si>
+  <si>
+    <t>REF399567</t>
+  </si>
+  <si>
+    <t>REF502128</t>
+  </si>
+  <si>
+    <t>REF592418</t>
+  </si>
+  <si>
+    <t>REF451565</t>
+  </si>
+  <si>
+    <t>REF979569</t>
+  </si>
+  <si>
+    <t>REF691890</t>
+  </si>
+  <si>
+    <t>REF458460</t>
+  </si>
+  <si>
+    <t>REF766036</t>
+  </si>
+  <si>
+    <t>REF892090</t>
+  </si>
+  <si>
+    <t>REF170682</t>
+  </si>
+  <si>
+    <t>REF848897</t>
+  </si>
+  <si>
+    <t>REF360967</t>
+  </si>
+  <si>
+    <t>REF534168</t>
+  </si>
+  <si>
+    <t>REF202119</t>
+  </si>
+  <si>
+    <t>REF147816</t>
+  </si>
+  <si>
+    <t>REF126083</t>
+  </si>
+  <si>
+    <t>REF558559</t>
+  </si>
+  <si>
+    <t>REF588337</t>
+  </si>
+  <si>
+    <t>REF777416</t>
+  </si>
+  <si>
+    <t>REF198215</t>
+  </si>
+  <si>
+    <t>REF892021</t>
+  </si>
+  <si>
+    <t>REF634118</t>
   </si>
   <si>
     <t>REF945644</t>
   </si>
   <si>
-    <t>Saving</t>
-  </si>
-  <si>
-    <t>000301</t>
-  </si>
-  <si>
-    <t>Delayed</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>290629</t>
-  </si>
-  <si>
-    <t>10092025F9012</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Morning</t>
-  </si>
-  <si>
-    <t>Curd 500g</t>
-  </si>
-  <si>
-    <t>CURD500</t>
-  </si>
-  <si>
-    <t>REF777416</t>
-  </si>
-  <si>
-    <t>On-Time</t>
-  </si>
-  <si>
-    <t>Doen</t>
-  </si>
-  <si>
-    <t>Paneer 200g</t>
-  </si>
-  <si>
-    <t>PNR200</t>
-  </si>
-  <si>
-    <t>REF147816</t>
-  </si>
-  <si>
-    <t>Buffalo</t>
-  </si>
-  <si>
-    <t>REF848897</t>
-  </si>
-  <si>
-    <t>REF458460</t>
-  </si>
-  <si>
-    <t>Mix</t>
-  </si>
-  <si>
-    <t>REF592418</t>
-  </si>
-  <si>
-    <t>REF741789</t>
-  </si>
-  <si>
-    <t>REF228007</t>
-  </si>
-  <si>
-    <t>REF704684</t>
-  </si>
-  <si>
-    <t>REF184826</t>
-  </si>
-  <si>
-    <t>Ramesh Patel</t>
-  </si>
-  <si>
-    <t>F9013</t>
-  </si>
-  <si>
-    <t>Anand</t>
-  </si>
-  <si>
-    <t>HDFC000145</t>
-  </si>
-  <si>
-    <t>502334112233</t>
-  </si>
-  <si>
     <t>REF285268</t>
   </si>
   <si>
-    <t>001145</t>
-  </si>
-  <si>
-    <t>290630</t>
-  </si>
-  <si>
-    <t>10092025F9013</t>
-  </si>
-  <si>
-    <t>Ghee 1L</t>
-  </si>
-  <si>
-    <t>GHEE1L</t>
-  </si>
-  <si>
-    <t>REF198215</t>
-  </si>
-  <si>
-    <t>REF126083</t>
-  </si>
-  <si>
-    <t>REF360967</t>
-  </si>
-  <si>
-    <t>REF766036</t>
-  </si>
-  <si>
-    <t>REF451565</t>
-  </si>
-  <si>
-    <t>REF540642</t>
-  </si>
-  <si>
-    <t>REF467823</t>
-  </si>
-  <si>
-    <t>REF687808</t>
-  </si>
-  <si>
-    <t>REF942636</t>
-  </si>
-  <si>
-    <t>Kiran Desai</t>
-  </si>
-  <si>
-    <t>F9014</t>
-  </si>
-  <si>
-    <t>Nadiyad</t>
-  </si>
-  <si>
-    <t>ICIC000287</t>
-  </si>
-  <si>
-    <t>721009988776</t>
-  </si>
-  <si>
     <t>REF248908</t>
   </si>
   <si>
-    <t>002287</t>
-  </si>
-  <si>
-    <t>290631</t>
-  </si>
-  <si>
-    <t>10092025F9014</t>
-  </si>
-  <si>
-    <t>REF892021</t>
-  </si>
-  <si>
-    <t>REF558559</t>
-  </si>
-  <si>
-    <t>REF534168</t>
-  </si>
-  <si>
-    <t>REF892090</t>
-  </si>
-  <si>
-    <t>REF979569</t>
-  </si>
-  <si>
-    <t>REF399567</t>
-  </si>
-  <si>
-    <t>REF511813</t>
-  </si>
-  <si>
-    <t>REF526880</t>
-  </si>
-  <si>
-    <t>REF711630</t>
-  </si>
-  <si>
-    <t>Amit Shah</t>
-  </si>
-  <si>
-    <t>F9015</t>
-  </si>
-  <si>
-    <t>Vadodara</t>
-  </si>
-  <si>
-    <t>BOB000119</t>
-  </si>
-  <si>
-    <t>336699002211</t>
-  </si>
-  <si>
     <t>REF479957</t>
-  </si>
-  <si>
-    <t>001119</t>
-  </si>
-  <si>
-    <t>290632</t>
-  </si>
-  <si>
-    <t>10092025F9015</t>
-  </si>
-  <si>
-    <t>REF634118</t>
-  </si>
-  <si>
-    <t>REF588337</t>
-  </si>
-  <si>
-    <t>REF202119</t>
-  </si>
-  <si>
-    <t>REF170682</t>
-  </si>
-  <si>
-    <t>REF691890</t>
-  </si>
-  <si>
-    <t>REF502128</t>
-  </si>
-  <si>
-    <t>REF262971</t>
-  </si>
-  <si>
-    <t>REF713190</t>
-  </si>
-  <si>
-    <t>REF254738</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1106,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1137,7 +1125,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="190500"/>
+          <a:off x="21955125" y="190500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1149,7 +1137,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1168,7 +1156,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="381000"/>
+          <a:off x="21955125" y="381000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1180,7 +1168,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1199,7 +1187,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="571500"/>
+          <a:off x="21955125" y="571500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1211,7 +1199,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1230,7 +1218,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="762000"/>
+          <a:off x="21955125" y="762000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1242,7 +1230,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1261,7 +1249,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="952500"/>
+          <a:off x="21955125" y="952500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1273,7 +1261,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1292,7 +1280,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="1143000"/>
+          <a:off x="21955125" y="1143000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1304,7 +1292,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1323,7 +1311,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="1333500"/>
+          <a:off x="21955125" y="1333500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1335,7 +1323,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1354,7 +1342,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="1524000"/>
+          <a:off x="21955125" y="1524000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1366,7 +1354,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1385,7 +1373,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="1714500"/>
+          <a:off x="21955125" y="1714500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1397,7 +1385,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1416,7 +1404,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="1905000"/>
+          <a:off x="21955125" y="1905000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1428,7 +1416,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1447,7 +1435,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="2095500"/>
+          <a:off x="21955125" y="2095500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1459,7 +1447,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1478,7 +1466,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="2286000"/>
+          <a:off x="21955125" y="2286000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1490,7 +1478,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1509,7 +1497,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="2476500"/>
+          <a:off x="21955125" y="2476500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1521,7 +1509,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1540,7 +1528,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="2667000"/>
+          <a:off x="21955125" y="2667000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1552,7 +1540,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1571,7 +1559,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="2857500"/>
+          <a:off x="21955125" y="2857500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1583,7 +1571,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1602,7 +1590,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="3048000"/>
+          <a:off x="21955125" y="3048000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1614,7 +1602,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1633,7 +1621,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="3238500"/>
+          <a:off x="21955125" y="3238500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1645,7 +1633,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1664,7 +1652,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="3429000"/>
+          <a:off x="21955125" y="3429000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1676,7 +1664,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1695,7 +1683,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="3619500"/>
+          <a:off x="21955125" y="3619500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1707,7 +1695,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1726,7 +1714,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="3810000"/>
+          <a:off x="21955125" y="3810000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1738,7 +1726,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1757,7 +1745,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4000500"/>
+          <a:off x="21955125" y="4000500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1769,7 +1757,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1788,7 +1776,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4191000"/>
+          <a:off x="21955125" y="4191000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1800,7 +1788,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1819,7 +1807,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4381500"/>
+          <a:off x="21955125" y="4381500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1831,7 +1819,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1850,7 +1838,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4572000"/>
+          <a:off x="21955125" y="4572000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1862,7 +1850,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1881,7 +1869,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4762500"/>
+          <a:off x="21955125" y="4762500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1893,7 +1881,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1912,7 +1900,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="4953000"/>
+          <a:off x="21955125" y="4953000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1924,7 +1912,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1943,7 +1931,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="5143500"/>
+          <a:off x="21955125" y="5143500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1955,7 +1943,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1974,7 +1962,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="5334000"/>
+          <a:off x="21955125" y="5334000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1986,7 +1974,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2005,7 +1993,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="5524500"/>
+          <a:off x="21955125" y="5524500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2017,7 +2005,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2036,7 +2024,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="5715000"/>
+          <a:off x="21955125" y="5715000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2048,7 +2036,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2067,7 +2055,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="5905500"/>
+          <a:off x="21955125" y="5905500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2079,7 +2067,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2098,7 +2086,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="6096000"/>
+          <a:off x="21955125" y="6096000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2110,7 +2098,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2129,7 +2117,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="6286500"/>
+          <a:off x="21955125" y="6286500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2141,7 +2129,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2160,7 +2148,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="6477000"/>
+          <a:off x="21955125" y="6477000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2172,7 +2160,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2191,7 +2179,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="6667500"/>
+          <a:off x="21955125" y="6667500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2203,7 +2191,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2222,7 +2210,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="6858000"/>
+          <a:off x="21955125" y="6858000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2234,7 +2222,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2253,7 +2241,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="7048500"/>
+          <a:off x="21955125" y="7048500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2265,7 +2253,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2284,7 +2272,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="7239000"/>
+          <a:off x="21955125" y="7239000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2296,7 +2284,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2315,7 +2303,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="7429500"/>
+          <a:off x="21955125" y="7429500"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2327,7 +2315,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2346,7 +2334,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21497925" y="7620000"/>
+          <a:off x="21955125" y="7620000"/>
           <a:ext cx="904875" cy="904875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2644,18 +2632,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH41"/>
+  <dimension ref="A1:AG41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="10.8571428571429" customWidth="1"/>
-    <col min="17" max="17" width="17.2857142857143" customWidth="1"/>
+    <col min="17" max="17" width="27.8571428571429" customWidth="1"/>
     <col min="20" max="20" width="11.7142857142857" customWidth="1"/>
-    <col min="21" max="21" width="11.5714285714286" customWidth="1"/>
+    <col min="21" max="21" width="12.4285714285714" customWidth="1"/>
     <col min="28" max="28" width="12.8571428571429" customWidth="1"/>
-    <col min="32" max="32" width="15.1428571428571" customWidth="1"/>
+    <col min="30" max="30" width="13.4285714285714" customWidth="1"/>
+    <col min="31" max="31" width="15.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2752,144 +2741,138 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2">
+        <v>45910</v>
+      </c>
+      <c r="F2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2">
-        <v>45901</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
       <c r="H2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="I2">
-        <v>5.06</v>
+        <v>4.68</v>
       </c>
       <c r="J2">
-        <v>8.24</v>
+        <v>8.22</v>
       </c>
       <c r="K2">
         <v>34</v>
       </c>
       <c r="L2">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="M2">
-        <v>33.6</v>
+        <v>33.9</v>
       </c>
       <c r="N2">
-        <v>2837.2</v>
+        <v>3646.4</v>
       </c>
       <c r="O2">
-        <v>2755.2</v>
+        <v>3593.4</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <v>45903</v>
+        <v>45912</v>
       </c>
       <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" s="2">
+        <v>45910</v>
+      </c>
+      <c r="U2" s="2">
+        <v>45915</v>
+      </c>
+      <c r="V2" t="s">
         <v>41</v>
-      </c>
-      <c r="T2" s="2">
-        <v>45901</v>
-      </c>
-      <c r="U2" s="2">
-        <v>45906</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
       </c>
       <c r="W2">
         <v>4.3</v>
       </c>
       <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>45</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>49</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>50</v>
       </c>
-      <c r="AF2" t="s">
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" t="s">
         <v>51</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:33">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
       <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2">
+        <v>45910</v>
+      </c>
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2">
-        <v>45902</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>4.37</v>
       </c>
       <c r="J3">
-        <v>8.4</v>
+        <v>8.16</v>
       </c>
       <c r="K3">
         <v>34</v>
@@ -2898,705 +2881,684 @@
         <v>34.2</v>
       </c>
       <c r="M3">
-        <v>34.7</v>
+        <v>33.2</v>
       </c>
       <c r="N3">
-        <v>2736</v>
+        <v>2907</v>
       </c>
       <c r="O3">
-        <v>2776</v>
+        <v>2822</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="R3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T3" s="2">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="U3" s="2">
-        <v>45907</v>
+        <v>45915</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Y3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="Z3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC3" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" t="s">
-        <v>57</v>
-      </c>
       <c r="AD3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF3" t="s">
         <v>50</v>
       </c>
-      <c r="AF3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="2">
+        <v>45910</v>
+      </c>
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="2">
-        <v>45903</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
-        <v>8.24</v>
+        <v>8.41</v>
       </c>
       <c r="K4">
         <v>34</v>
       </c>
       <c r="L4">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="M4">
-        <v>33.5</v>
+        <v>34.2</v>
       </c>
       <c r="N4">
-        <v>3740</v>
+        <v>3420</v>
       </c>
       <c r="O4">
-        <v>3685</v>
+        <v>3420</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>45905</v>
+        <v>45912</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="S4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="T4" s="2">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="U4" s="2">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="V4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W4">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="X4" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Y4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="Z4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC4" t="s">
         <v>47</v>
       </c>
-      <c r="AC4" t="s">
-        <v>48</v>
-      </c>
       <c r="AD4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF4" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
       <c r="E5" s="2">
-        <v>45904</v>
+        <v>45910</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I5">
-        <v>5.08</v>
+        <v>3.85</v>
       </c>
       <c r="J5">
-        <v>8.1</v>
+        <v>8.52</v>
       </c>
       <c r="K5">
         <v>34</v>
       </c>
       <c r="L5">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="M5">
-        <v>33.6</v>
+        <v>32.9</v>
       </c>
       <c r="N5">
-        <v>3460</v>
+        <v>3288.3</v>
       </c>
       <c r="O5">
-        <v>3360</v>
+        <v>3191.3</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <v>45906</v>
+        <v>45912</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T5" s="2">
-        <v>45904</v>
+        <v>45910</v>
       </c>
       <c r="U5" s="2">
+        <v>45915</v>
+      </c>
+      <c r="V5" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5">
+        <v>4.3</v>
+      </c>
+      <c r="X5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2">
         <v>45909</v>
       </c>
-      <c r="V5" t="s">
-        <v>42</v>
-      </c>
-      <c r="W5">
-        <v>4.6</v>
-      </c>
-      <c r="X5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2">
-        <v>45905</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H6">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I6">
-        <v>4.86</v>
+        <v>4.07</v>
       </c>
       <c r="J6">
-        <v>8.65</v>
+        <v>8.57</v>
       </c>
       <c r="K6">
         <v>34</v>
       </c>
       <c r="L6">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N6">
-        <v>3070.5</v>
+        <v>3264</v>
       </c>
       <c r="O6">
-        <v>3115</v>
+        <v>3264</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>45907</v>
+        <v>45912</v>
       </c>
       <c r="R6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="S6" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6" s="2">
+        <v>45909</v>
+      </c>
+      <c r="U6" s="2">
+        <v>45914</v>
+      </c>
+      <c r="V6" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="2">
-        <v>45905</v>
-      </c>
-      <c r="U6" s="2">
-        <v>45910</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6">
+        <v>3.8</v>
+      </c>
+      <c r="X6" t="s">
         <v>42</v>
       </c>
-      <c r="W6">
-        <v>4.5</v>
-      </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>43</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
       <c r="Z6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="AA6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB6" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>47</v>
       </c>
-      <c r="AC6" t="s">
-        <v>57</v>
-      </c>
       <c r="AD6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" t="s">
         <v>49</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>50</v>
       </c>
-      <c r="AF6" t="s">
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" t="s">
         <v>51</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:33">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
       <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
       <c r="E7" s="2">
-        <v>45906</v>
+        <v>45909</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H7">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I7">
-        <v>4.32</v>
+        <v>4.91</v>
       </c>
       <c r="J7">
-        <v>8.81</v>
+        <v>8.2</v>
       </c>
       <c r="K7">
         <v>34</v>
       </c>
       <c r="L7">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="M7">
-        <v>34.7</v>
+        <v>34</v>
       </c>
       <c r="N7">
-        <v>2257.2</v>
+        <v>2484</v>
       </c>
       <c r="O7">
-        <v>2290.2</v>
+        <v>2448</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="R7" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="S7" t="s">
+        <v>67</v>
+      </c>
+      <c r="T7" s="2">
+        <v>45909</v>
+      </c>
+      <c r="U7" s="2">
+        <v>45914</v>
+      </c>
+      <c r="V7" t="s">
         <v>41</v>
       </c>
-      <c r="T7" s="2">
-        <v>45906</v>
-      </c>
-      <c r="U7" s="2">
-        <v>45911</v>
-      </c>
-      <c r="V7" t="s">
-        <v>42</v>
-      </c>
       <c r="W7">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="X7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Y7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="Z7" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="AA7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC7" t="s">
         <v>47</v>
       </c>
-      <c r="AC7" t="s">
-        <v>57</v>
-      </c>
       <c r="AD7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF7" t="s">
         <v>50</v>
       </c>
-      <c r="AF7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
       <c r="E8" s="2">
-        <v>45907</v>
+        <v>45909</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H8">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="I8">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="J8">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="K8">
         <v>34</v>
       </c>
       <c r="L8">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M8">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="N8">
-        <v>2830.3</v>
+        <v>4035.6</v>
       </c>
       <c r="O8">
-        <v>2830.3</v>
+        <v>4035.6</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" t="s">
+        <v>40</v>
+      </c>
+      <c r="T8" s="2">
         <v>45909</v>
       </c>
-      <c r="R8" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" t="s">
-        <v>55</v>
-      </c>
-      <c r="T8" s="2">
-        <v>45907</v>
-      </c>
       <c r="U8" s="2">
-        <v>45912</v>
+        <v>45914</v>
       </c>
       <c r="V8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W8">
         <v>4.5</v>
       </c>
       <c r="X8" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="Y8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="Z8" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="AA8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC8" t="s">
         <v>47</v>
       </c>
-      <c r="AC8" t="s">
-        <v>57</v>
-      </c>
       <c r="AD8" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AE8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF8" t="s">
         <v>50</v>
       </c>
-      <c r="AF8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
       <c r="E9" s="2">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H9">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I9">
-        <v>3.96</v>
+        <v>5.1</v>
       </c>
       <c r="J9">
-        <v>8.36</v>
+        <v>8.61</v>
       </c>
       <c r="K9">
         <v>34</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>34.7</v>
       </c>
       <c r="M9">
-        <v>34</v>
+        <v>35.2</v>
       </c>
       <c r="N9">
-        <v>2992</v>
+        <v>2463.7</v>
       </c>
       <c r="O9">
-        <v>2992</v>
+        <v>2499.2</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="R9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="S9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="T9" s="2">
+        <v>45909</v>
+      </c>
+      <c r="U9" s="2">
+        <v>45914</v>
+      </c>
+      <c r="V9" t="s">
+        <v>41</v>
+      </c>
+      <c r="W9">
+        <v>4.8</v>
+      </c>
+      <c r="X9" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2">
         <v>45908</v>
       </c>
-      <c r="U9" s="2">
-        <v>45913</v>
-      </c>
-      <c r="V9" t="s">
-        <v>42</v>
-      </c>
-      <c r="W9">
-        <v>3.8</v>
-      </c>
-      <c r="X9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2">
-        <v>45909</v>
-      </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I10">
-        <v>4.07</v>
+        <v>3.96</v>
       </c>
       <c r="J10">
-        <v>8.57</v>
+        <v>8.36</v>
       </c>
       <c r="K10">
         <v>34</v>
@@ -3608,111 +3570,108 @@
         <v>34</v>
       </c>
       <c r="N10">
-        <v>3264</v>
+        <v>2992</v>
       </c>
       <c r="O10">
-        <v>3264</v>
+        <v>2992</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="R10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s">
         <v>40</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" s="2">
+        <v>45908</v>
+      </c>
+      <c r="U10" s="2">
+        <v>45913</v>
+      </c>
+      <c r="V10" t="s">
         <v>41</v>
-      </c>
-      <c r="T10" s="2">
-        <v>45909</v>
-      </c>
-      <c r="U10" s="2">
-        <v>45914</v>
-      </c>
-      <c r="V10" t="s">
-        <v>42</v>
       </c>
       <c r="W10">
         <v>3.8</v>
       </c>
       <c r="X10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y10" t="s">
         <v>43</v>
       </c>
-      <c r="Y10" t="s">
-        <v>44</v>
-      </c>
       <c r="Z10" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="AA10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB10" t="s">
         <v>46</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>47</v>
       </c>
-      <c r="AC10" t="s">
-        <v>57</v>
-      </c>
       <c r="AD10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE10" t="s">
         <v>49</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>50</v>
       </c>
-      <c r="AF10" t="s">
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" t="s">
         <v>51</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="B11" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:33">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
       <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
       <c r="E11" s="2">
-        <v>45910</v>
+        <v>45908</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H11">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I11">
-        <v>4.68</v>
+        <v>4.36</v>
       </c>
       <c r="J11">
-        <v>8.22</v>
+        <v>8.47</v>
       </c>
       <c r="K11">
         <v>34</v>
       </c>
       <c r="L11">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="M11">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="N11">
-        <v>3646.4</v>
+        <v>3693.6</v>
       </c>
       <c r="O11">
-        <v>3593.4</v>
+        <v>3639.6</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3721,892 +3680,865 @@
         <v>45912</v>
       </c>
       <c r="R11" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" s="2">
+        <v>45908</v>
+      </c>
+      <c r="U11" s="2">
+        <v>45913</v>
+      </c>
+      <c r="V11" t="s">
+        <v>41</v>
+      </c>
+      <c r="W11">
+        <v>3.8</v>
+      </c>
+      <c r="X11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB11" t="s">
         <v>60</v>
       </c>
-      <c r="T11" s="2">
-        <v>45910</v>
-      </c>
-      <c r="U11" s="2">
-        <v>45915</v>
-      </c>
-      <c r="V11" t="s">
-        <v>42</v>
-      </c>
-      <c r="W11">
-        <v>4.3</v>
-      </c>
-      <c r="X11" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>47</v>
       </c>
-      <c r="AC11" t="s">
-        <v>48</v>
-      </c>
       <c r="AD11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF11" t="s">
         <v>50</v>
       </c>
-      <c r="AF11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2">
-        <v>45901</v>
+        <v>45908</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H12">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="I12">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="J12">
-        <v>8.7</v>
+        <v>8.8</v>
       </c>
       <c r="K12">
         <v>34</v>
       </c>
       <c r="L12">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="M12">
-        <v>34.6</v>
+        <v>33.5</v>
       </c>
       <c r="N12">
-        <v>3375.9</v>
+        <v>2278</v>
       </c>
       <c r="O12">
-        <v>3425.4</v>
+        <v>2244.5</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12" s="2">
-        <v>45903</v>
+        <v>45912</v>
       </c>
       <c r="R12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S12" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="T12" s="2">
-        <v>45901</v>
+        <v>45908</v>
       </c>
       <c r="U12" s="2">
-        <v>45906</v>
+        <v>45913</v>
       </c>
       <c r="V12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="X12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" t="s">
         <v>74</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="B13" t="s">
         <v>75</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="AA12" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45908</v>
+      </c>
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="AC12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE12" t="s">
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="AF12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33">
-      <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2">
-        <v>45902</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>65</v>
-      </c>
       <c r="H13">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I13">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="J13">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="K13">
         <v>34</v>
       </c>
       <c r="L13">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="M13">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="N13">
-        <v>2992.8</v>
+        <v>3967.2</v>
       </c>
       <c r="O13">
-        <v>2905.8</v>
+        <v>3909.2</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="R13" t="s">
+        <v>79</v>
+      </c>
+      <c r="S13" t="s">
         <v>80</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" s="2">
+        <v>45908</v>
+      </c>
+      <c r="U13" s="2">
+        <v>45913</v>
+      </c>
+      <c r="V13" t="s">
+        <v>41</v>
+      </c>
+      <c r="W13">
+        <v>3.9</v>
+      </c>
+      <c r="X13" t="s">
         <v>81</v>
       </c>
-      <c r="T13" s="2">
-        <v>45902</v>
-      </c>
-      <c r="U13" s="2">
+      <c r="Y13" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="2">
         <v>45907</v>
       </c>
-      <c r="V13" t="s">
-        <v>42</v>
-      </c>
-      <c r="W13">
-        <v>4.1</v>
-      </c>
-      <c r="X13" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33">
-      <c r="A14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="2">
-        <v>45903</v>
-      </c>
-      <c r="F14" t="s">
-        <v>38</v>
-      </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H14">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="I14">
-        <v>4.66</v>
+        <v>4.18</v>
       </c>
       <c r="J14">
-        <v>8.57</v>
+        <v>8.18</v>
       </c>
       <c r="K14">
         <v>34</v>
       </c>
       <c r="L14">
-        <v>34.4</v>
+        <v>34.1</v>
       </c>
       <c r="M14">
-        <v>34.9</v>
+        <v>34.1</v>
       </c>
       <c r="N14">
-        <v>3680.8</v>
+        <v>2830.3</v>
       </c>
       <c r="O14">
-        <v>3734.3</v>
+        <v>2830.3</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14" s="2">
-        <v>45905</v>
+        <v>45912</v>
       </c>
       <c r="R14" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="T14" s="2">
-        <v>45903</v>
+        <v>45907</v>
       </c>
       <c r="U14" s="2">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="V14" t="s">
+        <v>41</v>
+      </c>
+      <c r="W14">
+        <v>4.5</v>
+      </c>
+      <c r="X14" t="s">
         <v>42</v>
       </c>
-      <c r="W14">
-        <v>3.9</v>
-      </c>
-      <c r="X14" t="s">
-        <v>74</v>
-      </c>
       <c r="Y14" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="Z14" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB14" t="s">
         <v>46</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45907</v>
+      </c>
+      <c r="F15" t="s">
         <v>77</v>
       </c>
-      <c r="AC14" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="2">
-        <v>45904</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>38</v>
       </c>
-      <c r="G15" t="s">
-        <v>62</v>
-      </c>
       <c r="H15">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="I15">
-        <v>4.96</v>
+        <v>4.25</v>
       </c>
       <c r="J15">
-        <v>8.36</v>
+        <v>8.03</v>
       </c>
       <c r="K15">
         <v>34</v>
       </c>
       <c r="L15">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="M15">
-        <v>34.1</v>
+        <v>33.1</v>
       </c>
       <c r="N15">
-        <v>4013.6</v>
+        <v>2591.6</v>
       </c>
       <c r="O15">
-        <v>3955.6</v>
+        <v>2515.6</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15" s="2">
-        <v>45906</v>
+        <v>45912</v>
       </c>
       <c r="R15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="T15" s="2">
-        <v>45904</v>
+        <v>45907</v>
       </c>
       <c r="U15" s="2">
-        <v>45909</v>
+        <v>45912</v>
       </c>
       <c r="V15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W15">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="Y15" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="Z15" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AA15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB15" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="AC15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE15" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="AF15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45907</v>
+      </c>
+      <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="2">
-        <v>45905</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>38</v>
       </c>
-      <c r="G16" t="s">
-        <v>62</v>
-      </c>
       <c r="H16">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="I16">
-        <v>4.83</v>
+        <v>3.9</v>
       </c>
       <c r="J16">
-        <v>8.52</v>
+        <v>8.73</v>
       </c>
       <c r="K16">
         <v>34</v>
       </c>
       <c r="L16">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="M16">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="N16">
-        <v>3208.5</v>
+        <v>3457.8</v>
       </c>
       <c r="O16">
-        <v>3162</v>
+        <v>3406.8</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R16" t="s">
+        <v>79</v>
+      </c>
+      <c r="S16" t="s">
+        <v>80</v>
+      </c>
+      <c r="T16" s="2">
         <v>45907</v>
       </c>
-      <c r="R16" t="s">
-        <v>80</v>
-      </c>
-      <c r="S16" t="s">
-        <v>81</v>
-      </c>
-      <c r="T16" s="2">
-        <v>45905</v>
-      </c>
       <c r="U16" s="2">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="V16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W16">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" t="s">
         <v>74</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="B17" t="s">
         <v>75</v>
       </c>
-      <c r="Z16" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45907</v>
+      </c>
+      <c r="F17" t="s">
         <v>77</v>
       </c>
-      <c r="AC16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE16">
-        <v>290630</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
-      <c r="A17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="2">
-        <v>45906</v>
-      </c>
-      <c r="F17" t="s">
-        <v>38</v>
-      </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H17">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I17">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="J17">
-        <v>8.72</v>
+        <v>8.59</v>
       </c>
       <c r="K17">
         <v>34</v>
       </c>
       <c r="L17">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="M17">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="N17">
-        <v>2659.8</v>
+        <v>2278</v>
       </c>
       <c r="O17">
-        <v>2581.8</v>
+        <v>2244.5</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17" s="2">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="R17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="S17" t="s">
+        <v>67</v>
+      </c>
+      <c r="T17" s="2">
+        <v>45907</v>
+      </c>
+      <c r="U17" s="2">
+        <v>45912</v>
+      </c>
+      <c r="V17" t="s">
+        <v>41</v>
+      </c>
+      <c r="W17">
+        <v>4.7</v>
+      </c>
+      <c r="X17" t="s">
         <v>81</v>
       </c>
-      <c r="T17" s="2">
+      <c r="Y17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2">
         <v>45906</v>
       </c>
-      <c r="U17" s="2">
-        <v>45911</v>
-      </c>
-      <c r="V17" t="s">
-        <v>42</v>
-      </c>
-      <c r="W17">
-        <v>4.4</v>
-      </c>
-      <c r="X17" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
-      <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="2">
-        <v>45907</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H18">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I18">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="J18">
-        <v>8.03</v>
+        <v>8.81</v>
       </c>
       <c r="K18">
         <v>34</v>
       </c>
       <c r="L18">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M18">
-        <v>33.1</v>
+        <v>34.7</v>
       </c>
       <c r="N18">
-        <v>2591.6</v>
+        <v>2257.2</v>
       </c>
       <c r="O18">
-        <v>2515.6</v>
+        <v>2290.2</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18" s="2">
-        <v>45909</v>
+        <v>45912</v>
       </c>
       <c r="R18" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="S18" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="T18" s="2">
-        <v>45907</v>
+        <v>45906</v>
       </c>
       <c r="U18" s="2">
-        <v>45912</v>
+        <v>45911</v>
       </c>
       <c r="V18" t="s">
+        <v>41</v>
+      </c>
+      <c r="W18">
+        <v>4.2</v>
+      </c>
+      <c r="X18" t="s">
         <v>42</v>
       </c>
-      <c r="W18">
-        <v>4.1</v>
-      </c>
-      <c r="X18" t="s">
-        <v>74</v>
-      </c>
       <c r="Y18" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="Z18" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="AA18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB18" t="s">
         <v>46</v>
       </c>
-      <c r="AB18" t="s">
-        <v>77</v>
-      </c>
       <c r="AC18" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD18" t="s">
         <v>48</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AE18" t="s">
         <v>49</v>
       </c>
-      <c r="AE18" t="s">
+      <c r="AF18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45906</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" t="s">
         <v>78</v>
       </c>
-      <c r="AF18" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
-      <c r="A19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="2">
-        <v>45908</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>62</v>
-      </c>
       <c r="H19">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="I19">
-        <v>4.36</v>
+        <v>4.12</v>
       </c>
       <c r="J19">
-        <v>8.47</v>
+        <v>8.72</v>
       </c>
       <c r="K19">
         <v>34</v>
       </c>
       <c r="L19">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M19">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="N19">
-        <v>3693.6</v>
+        <v>2659.8</v>
       </c>
       <c r="O19">
-        <v>3639.6</v>
+        <v>2581.8</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19" s="2">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="R19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="T19" s="2">
-        <v>45908</v>
+        <v>45906</v>
       </c>
       <c r="U19" s="2">
-        <v>45913</v>
+        <v>45911</v>
       </c>
       <c r="V19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W19">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="X19" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="Y19" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="Z19" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AA19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45906</v>
+      </c>
+      <c r="F20" t="s">
         <v>77</v>
       </c>
-      <c r="AC19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
-      <c r="A20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="2">
-        <v>45909</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H20">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I20">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="J20">
-        <v>8.2</v>
+        <v>8.87</v>
       </c>
       <c r="K20">
         <v>34</v>
@@ -4615,114 +4547,111 @@
         <v>34.5</v>
       </c>
       <c r="M20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N20">
-        <v>2484</v>
+        <v>2277</v>
       </c>
       <c r="O20">
-        <v>2448</v>
+        <v>2310</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R20" t="s">
+        <v>66</v>
+      </c>
+      <c r="S20" t="s">
+        <v>67</v>
+      </c>
+      <c r="T20" s="2">
+        <v>45906</v>
+      </c>
+      <c r="U20" s="2">
         <v>45911</v>
       </c>
-      <c r="R20" t="s">
-        <v>80</v>
-      </c>
-      <c r="S20" t="s">
-        <v>81</v>
-      </c>
-      <c r="T20" s="2">
-        <v>45909</v>
-      </c>
-      <c r="U20" s="2">
-        <v>45914</v>
-      </c>
       <c r="V20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W20">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="X20" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
+      <c r="A21" t="s">
         <v>74</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="B21" t="s">
         <v>75</v>
       </c>
-      <c r="Z20" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45906</v>
+      </c>
+      <c r="F21" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="2">
-        <v>45910</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>38</v>
       </c>
-      <c r="G21" t="s">
-        <v>65</v>
-      </c>
       <c r="H21">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="I21">
-        <v>4.37</v>
+        <v>4.8</v>
       </c>
       <c r="J21">
-        <v>8.16</v>
+        <v>8.46</v>
       </c>
       <c r="K21">
         <v>34</v>
       </c>
       <c r="L21">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="M21">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="N21">
-        <v>2907</v>
+        <v>3760.5</v>
       </c>
       <c r="O21">
-        <v>2822</v>
+        <v>3706</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4731,1008 +4660,978 @@
         <v>45912</v>
       </c>
       <c r="R21" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="S21" t="s">
+        <v>56</v>
+      </c>
+      <c r="T21" s="2">
+        <v>45906</v>
+      </c>
+      <c r="U21" s="2">
+        <v>45911</v>
+      </c>
+      <c r="V21" t="s">
         <v>41</v>
-      </c>
-      <c r="T21" s="2">
-        <v>45910</v>
-      </c>
-      <c r="U21" s="2">
-        <v>45915</v>
-      </c>
-      <c r="V21" t="s">
-        <v>42</v>
       </c>
       <c r="W21">
         <v>4.2</v>
       </c>
       <c r="X21" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Y21" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AA21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB21" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45905</v>
+      </c>
+      <c r="F22" t="s">
         <v>77</v>
       </c>
-      <c r="AC21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33">
-      <c r="A22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="2">
-        <v>45901</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>38</v>
       </c>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
       <c r="H22">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I22">
-        <v>4.97</v>
+        <v>4.86</v>
       </c>
       <c r="J22">
-        <v>8.39</v>
+        <v>8.65</v>
       </c>
       <c r="K22">
         <v>34</v>
       </c>
       <c r="L22">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="M22">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="N22">
-        <v>2664.2</v>
+        <v>3070.5</v>
       </c>
       <c r="O22">
-        <v>2702.7</v>
+        <v>3115</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22" s="2">
-        <v>45903</v>
+        <v>45912</v>
       </c>
       <c r="R22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="S22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="T22" s="2">
-        <v>45901</v>
+        <v>45905</v>
       </c>
       <c r="U22" s="2">
-        <v>45906</v>
+        <v>45910</v>
       </c>
       <c r="V22" t="s">
+        <v>41</v>
+      </c>
+      <c r="W22">
+        <v>4.5</v>
+      </c>
+      <c r="X22" t="s">
         <v>42</v>
       </c>
-      <c r="W22">
-        <v>3.9</v>
-      </c>
-      <c r="X22" t="s">
-        <v>94</v>
-      </c>
       <c r="Y22" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="Z22" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AA22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB22" t="s">
         <v>46</v>
       </c>
-      <c r="AB22" t="s">
-        <v>97</v>
-      </c>
       <c r="AC22" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD22" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE22" t="s">
         <v>49</v>
       </c>
-      <c r="AE22" t="s">
-        <v>98</v>
-      </c>
       <c r="AF22" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:33">
-      <c r="A23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
       <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45905</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23">
         <v>93</v>
       </c>
-      <c r="D23" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="2">
-        <v>45902</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23">
-        <v>104</v>
-      </c>
       <c r="I23">
-        <v>4.19</v>
+        <v>4.83</v>
       </c>
       <c r="J23">
-        <v>8.33</v>
+        <v>8.52</v>
       </c>
       <c r="K23">
         <v>34</v>
       </c>
       <c r="L23">
-        <v>34.1</v>
+        <v>34.5</v>
       </c>
       <c r="M23">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="N23">
-        <v>3546.4</v>
+        <v>3208.5</v>
       </c>
       <c r="O23">
-        <v>3546.4</v>
+        <v>3162</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23" s="2">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="R23" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S23" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="T23" s="2">
-        <v>45902</v>
+        <v>45905</v>
       </c>
       <c r="U23" s="2">
-        <v>45907</v>
+        <v>45910</v>
       </c>
       <c r="V23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X23" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="Y23" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="Z23" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD23">
+        <v>290630</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45905</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24">
         <v>100</v>
       </c>
-      <c r="AA23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE23">
-        <v>290631</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33">
-      <c r="A24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="2">
-        <v>45903</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24">
-        <v>117</v>
-      </c>
       <c r="I24">
-        <v>4.36</v>
+        <v>4.65</v>
       </c>
       <c r="J24">
-        <v>8.02</v>
+        <v>8.76</v>
       </c>
       <c r="K24">
         <v>34</v>
       </c>
       <c r="L24">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M24">
-        <v>33.2</v>
+        <v>34.4</v>
       </c>
       <c r="N24">
-        <v>4001.4</v>
+        <v>3440</v>
       </c>
       <c r="O24">
-        <v>3884.4</v>
+        <v>3440</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R24" t="s">
+        <v>55</v>
+      </c>
+      <c r="S24" t="s">
+        <v>56</v>
+      </c>
+      <c r="T24" s="2">
         <v>45905</v>
       </c>
-      <c r="R24" t="s">
-        <v>59</v>
-      </c>
-      <c r="S24" t="s">
-        <v>60</v>
-      </c>
-      <c r="T24" s="2">
-        <v>45903</v>
-      </c>
       <c r="U24" s="2">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="V24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W24">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="X24" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="Y24" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45905</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25">
         <v>95</v>
       </c>
-      <c r="Z24" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33">
-      <c r="A25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="2">
-        <v>45904</v>
-      </c>
-      <c r="F25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25">
-        <v>104</v>
-      </c>
       <c r="I25">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="J25">
-        <v>8.31</v>
+        <v>8.63</v>
       </c>
       <c r="K25">
         <v>34</v>
       </c>
       <c r="L25">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="M25">
-        <v>33.6</v>
+        <v>34.7</v>
       </c>
       <c r="N25">
-        <v>3598.4</v>
+        <v>3296.5</v>
       </c>
       <c r="O25">
-        <v>3494.4</v>
+        <v>3296.5</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25" s="2">
-        <v>45906</v>
+        <v>45912</v>
       </c>
       <c r="R25" t="s">
+        <v>79</v>
+      </c>
+      <c r="S25" t="s">
         <v>80</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" s="2">
+        <v>45905</v>
+      </c>
+      <c r="U25" s="2">
+        <v>45910</v>
+      </c>
+      <c r="V25" t="s">
+        <v>41</v>
+      </c>
+      <c r="W25">
+        <v>4.7</v>
+      </c>
+      <c r="X25" t="s">
         <v>81</v>
       </c>
-      <c r="T25" s="2">
+      <c r="Y25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2">
         <v>45904</v>
       </c>
-      <c r="U25" s="2">
-        <v>45909</v>
-      </c>
-      <c r="V25" t="s">
-        <v>42</v>
-      </c>
-      <c r="W25">
-        <v>4.6</v>
-      </c>
-      <c r="X25" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="2">
-        <v>45905</v>
-      </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26">
-        <v>4.65</v>
+        <v>5.08</v>
       </c>
       <c r="J26">
-        <v>8.76</v>
+        <v>8.1</v>
       </c>
       <c r="K26">
         <v>34</v>
       </c>
       <c r="L26">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="M26">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="N26">
-        <v>3440</v>
+        <v>3460</v>
       </c>
       <c r="O26">
-        <v>3440</v>
+        <v>3360</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26" s="2">
-        <v>45907</v>
+        <v>45912</v>
       </c>
       <c r="R26" t="s">
+        <v>39</v>
+      </c>
+      <c r="S26" t="s">
         <v>40</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" s="2">
+        <v>45904</v>
+      </c>
+      <c r="U26" s="2">
+        <v>45909</v>
+      </c>
+      <c r="V26" t="s">
         <v>41</v>
       </c>
-      <c r="T26" s="2">
-        <v>45905</v>
-      </c>
-      <c r="U26" s="2">
-        <v>45910</v>
-      </c>
-      <c r="V26" t="s">
+      <c r="W26">
+        <v>4.6</v>
+      </c>
+      <c r="X26" t="s">
         <v>42</v>
       </c>
-      <c r="W26">
-        <v>3.8</v>
-      </c>
-      <c r="X26" t="s">
-        <v>94</v>
-      </c>
       <c r="Y26" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="Z26" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AA26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB26" t="s">
         <v>46</v>
       </c>
-      <c r="AB26" t="s">
-        <v>97</v>
-      </c>
       <c r="AC26" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD26" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE26" t="s">
         <v>49</v>
       </c>
-      <c r="AE26" t="s">
-        <v>98</v>
-      </c>
       <c r="AF26" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="1:33">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45904</v>
+      </c>
+      <c r="F27" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="2">
-        <v>45906</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H27">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="I27">
-        <v>4.86</v>
+        <v>4.96</v>
       </c>
       <c r="J27">
-        <v>8.87</v>
+        <v>8.36</v>
       </c>
       <c r="K27">
         <v>34</v>
       </c>
       <c r="L27">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="M27">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="N27">
-        <v>2277</v>
+        <v>4013.6</v>
       </c>
       <c r="O27">
-        <v>2310</v>
+        <v>3955.6</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27" s="2">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="R27" t="s">
+        <v>79</v>
+      </c>
+      <c r="S27" t="s">
         <v>80</v>
       </c>
-      <c r="S27" t="s">
-        <v>81</v>
-      </c>
       <c r="T27" s="2">
-        <v>45906</v>
+        <v>45904</v>
       </c>
       <c r="U27" s="2">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="V27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W27">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X27" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="Y27" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="Z27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45904</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28">
         <v>104</v>
       </c>
-      <c r="AA27" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33">
-      <c r="A28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="2">
-        <v>45907</v>
-      </c>
-      <c r="F28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28">
-        <v>102</v>
-      </c>
       <c r="I28">
-        <v>3.9</v>
+        <v>4.97</v>
       </c>
       <c r="J28">
-        <v>8.73</v>
+        <v>8.31</v>
       </c>
       <c r="K28">
         <v>34</v>
       </c>
       <c r="L28">
-        <v>33.9</v>
+        <v>34.6</v>
       </c>
       <c r="M28">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="N28">
-        <v>3457.8</v>
+        <v>3598.4</v>
       </c>
       <c r="O28">
-        <v>3406.8</v>
+        <v>3494.4</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R28" t="s">
+        <v>66</v>
+      </c>
+      <c r="S28" t="s">
+        <v>67</v>
+      </c>
+      <c r="T28" s="2">
+        <v>45904</v>
+      </c>
+      <c r="U28" s="2">
         <v>45909</v>
       </c>
-      <c r="R28" t="s">
+      <c r="V28" t="s">
+        <v>41</v>
+      </c>
+      <c r="W28">
+        <v>4.6</v>
+      </c>
+      <c r="X28" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45904</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" t="s">
         <v>54</v>
       </c>
-      <c r="S28" t="s">
-        <v>55</v>
-      </c>
-      <c r="T28" s="2">
-        <v>45907</v>
-      </c>
-      <c r="U28" s="2">
-        <v>45912</v>
-      </c>
-      <c r="V28" t="s">
-        <v>42</v>
-      </c>
-      <c r="W28">
-        <v>4.1</v>
-      </c>
-      <c r="X28" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33">
-      <c r="A29" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="2">
-        <v>45908</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
-      </c>
       <c r="H29">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="I29">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="J29">
-        <v>8.8</v>
+        <v>8.4</v>
       </c>
       <c r="K29">
         <v>34</v>
       </c>
       <c r="L29">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="M29">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="N29">
-        <v>2278</v>
+        <v>3034.9</v>
       </c>
       <c r="O29">
-        <v>2244.5</v>
+        <v>2945.9</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" s="2">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="R29" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="S29" t="s">
+        <v>56</v>
+      </c>
+      <c r="T29" s="2">
+        <v>45904</v>
+      </c>
+      <c r="U29" s="2">
+        <v>45909</v>
+      </c>
+      <c r="V29" t="s">
+        <v>41</v>
+      </c>
+      <c r="W29">
+        <v>4.1</v>
+      </c>
+      <c r="X29" t="s">
         <v>81</v>
       </c>
-      <c r="T29" s="2">
-        <v>45908</v>
-      </c>
-      <c r="U29" s="2">
-        <v>45913</v>
-      </c>
-      <c r="V29" t="s">
-        <v>42</v>
-      </c>
-      <c r="W29">
-        <v>4.5</v>
-      </c>
-      <c r="X29" t="s">
-        <v>94</v>
-      </c>
       <c r="Y29" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AA29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB29" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AC29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD29" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="AE29" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="AF29" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:32">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" s="2">
-        <v>45909</v>
+        <v>45903</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H30">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I30">
-        <v>4.28</v>
+        <v>3.99</v>
       </c>
       <c r="J30">
-        <v>8.17</v>
+        <v>8.24</v>
       </c>
       <c r="K30">
         <v>34</v>
       </c>
       <c r="L30">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="M30">
-        <v>34.2</v>
+        <v>33.5</v>
       </c>
       <c r="N30">
-        <v>4035.6</v>
+        <v>3740</v>
       </c>
       <c r="O30">
-        <v>4035.6</v>
+        <v>3685</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30" s="2">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="R30" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="S30" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="T30" s="2">
-        <v>45909</v>
+        <v>45903</v>
       </c>
       <c r="U30" s="2">
-        <v>45914</v>
+        <v>45908</v>
       </c>
       <c r="V30" t="s">
+        <v>41</v>
+      </c>
+      <c r="W30">
+        <v>4.3</v>
+      </c>
+      <c r="X30" t="s">
         <v>42</v>
       </c>
-      <c r="W30">
-        <v>4.5</v>
-      </c>
-      <c r="X30" t="s">
-        <v>94</v>
-      </c>
       <c r="Y30" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="Z30" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="A31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45903</v>
+      </c>
+      <c r="F31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31">
         <v>107</v>
       </c>
-      <c r="AA30" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33">
-      <c r="A31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="2">
-        <v>45910</v>
-      </c>
-      <c r="F31" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" t="s">
-        <v>39</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
       <c r="I31">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="J31">
-        <v>8.41</v>
+        <v>8.57</v>
       </c>
       <c r="K31">
         <v>34</v>
       </c>
       <c r="L31">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M31">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="N31">
-        <v>3420</v>
+        <v>3680.8</v>
       </c>
       <c r="O31">
-        <v>3420</v>
+        <v>3734.3</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5741,1008 +5640,978 @@
         <v>45912</v>
       </c>
       <c r="R31" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="S31" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="T31" s="2">
-        <v>45910</v>
+        <v>45903</v>
       </c>
       <c r="U31" s="2">
-        <v>45915</v>
+        <v>45908</v>
       </c>
       <c r="V31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W31">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="X31" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="Y31" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="Z31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AA31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB31" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="AC31" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD31" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE31" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="AF31" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:32">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2">
-        <v>45901</v>
+        <v>45903</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H32">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I32">
-        <v>4.99</v>
+        <v>4.36</v>
       </c>
       <c r="J32">
-        <v>8.12</v>
+        <v>8.02</v>
       </c>
       <c r="K32">
         <v>34</v>
       </c>
       <c r="L32">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="M32">
-        <v>34.1</v>
+        <v>33.2</v>
       </c>
       <c r="N32">
-        <v>3667.6</v>
+        <v>4001.4</v>
       </c>
       <c r="O32">
-        <v>3614.6</v>
+        <v>3884.4</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R32" t="s">
+        <v>39</v>
+      </c>
+      <c r="S32" t="s">
+        <v>40</v>
+      </c>
+      <c r="T32" s="2">
         <v>45903</v>
       </c>
-      <c r="R32" t="s">
-        <v>54</v>
-      </c>
-      <c r="S32" t="s">
-        <v>55</v>
-      </c>
-      <c r="T32" s="2">
-        <v>45901</v>
-      </c>
       <c r="U32" s="2">
-        <v>45906</v>
+        <v>45908</v>
       </c>
       <c r="V32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W32">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="X32" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="Y32" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z32" t="s">
         <v>113</v>
       </c>
-      <c r="Z32" t="s">
-        <v>114</v>
-      </c>
       <c r="AA32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB32" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="AC32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD32" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AE32" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="AF32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:32">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H33">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I33">
-        <v>4.73</v>
+        <v>4.18</v>
       </c>
       <c r="J33">
-        <v>8.74</v>
+        <v>8.52</v>
       </c>
       <c r="K33">
         <v>34</v>
       </c>
       <c r="L33">
-        <v>34.4</v>
+        <v>34.1</v>
       </c>
       <c r="M33">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="N33">
-        <v>2339.2</v>
+        <v>2455.2</v>
       </c>
       <c r="O33">
-        <v>2305.2</v>
+        <v>2455.2</v>
       </c>
       <c r="P33">
         <v>0</v>
       </c>
       <c r="Q33" s="2">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="R33" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s">
+        <v>80</v>
+      </c>
+      <c r="T33" s="2">
+        <v>45903</v>
+      </c>
+      <c r="U33" s="2">
+        <v>45908</v>
+      </c>
+      <c r="V33" t="s">
         <v>41</v>
       </c>
-      <c r="T33" s="2">
+      <c r="W33">
+        <v>4.1</v>
+      </c>
+      <c r="X33" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="2">
         <v>45902</v>
       </c>
-      <c r="U33" s="2">
-        <v>45907</v>
-      </c>
-      <c r="V33" t="s">
-        <v>42</v>
-      </c>
-      <c r="W33">
-        <v>4.3</v>
-      </c>
-      <c r="X33" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33">
-      <c r="A34" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="2">
-        <v>45903</v>
-      </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H34">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I34">
-        <v>4.18</v>
+        <v>4.37</v>
       </c>
       <c r="J34">
-        <v>8.52</v>
+        <v>8.4</v>
       </c>
       <c r="K34">
         <v>34</v>
       </c>
       <c r="L34">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M34">
-        <v>34.1</v>
+        <v>34.7</v>
       </c>
       <c r="N34">
-        <v>2455.2</v>
+        <v>2736</v>
       </c>
       <c r="O34">
-        <v>2455.2</v>
+        <v>2776</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34" s="2">
-        <v>45905</v>
+        <v>45912</v>
       </c>
       <c r="R34" t="s">
+        <v>79</v>
+      </c>
+      <c r="S34" t="s">
+        <v>80</v>
+      </c>
+      <c r="T34" s="2">
+        <v>45902</v>
+      </c>
+      <c r="U34" s="2">
+        <v>45907</v>
+      </c>
+      <c r="V34" t="s">
+        <v>41</v>
+      </c>
+      <c r="W34">
+        <v>4.3</v>
+      </c>
+      <c r="X34" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45902</v>
+      </c>
+      <c r="F35" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" t="s">
         <v>54</v>
       </c>
-      <c r="S34" t="s">
-        <v>55</v>
-      </c>
-      <c r="T34" s="2">
-        <v>45903</v>
-      </c>
-      <c r="U34" s="2">
-        <v>45908</v>
-      </c>
-      <c r="V34" t="s">
-        <v>42</v>
-      </c>
-      <c r="W34">
-        <v>4.1</v>
-      </c>
-      <c r="X34" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33">
-      <c r="A35" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="2">
-        <v>45904</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" t="s">
-        <v>65</v>
-      </c>
       <c r="H35">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I35">
-        <v>4.12</v>
+        <v>4.59</v>
       </c>
       <c r="J35">
-        <v>8.4</v>
+        <v>8.16</v>
       </c>
       <c r="K35">
         <v>34</v>
       </c>
       <c r="L35">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="M35">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="N35">
-        <v>3034.9</v>
+        <v>2992.8</v>
       </c>
       <c r="O35">
-        <v>2945.9</v>
+        <v>2905.8</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35" s="2">
-        <v>45906</v>
+        <v>45912</v>
       </c>
       <c r="R35" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="S35" t="s">
+        <v>67</v>
+      </c>
+      <c r="T35" s="2">
+        <v>45902</v>
+      </c>
+      <c r="U35" s="2">
+        <v>45907</v>
+      </c>
+      <c r="V35" t="s">
         <v>41</v>
-      </c>
-      <c r="T35" s="2">
-        <v>45904</v>
-      </c>
-      <c r="U35" s="2">
-        <v>45909</v>
-      </c>
-      <c r="V35" t="s">
-        <v>42</v>
       </c>
       <c r="W35">
         <v>4.1</v>
       </c>
       <c r="X35" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="Y35" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="Z35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AA35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB35" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="AC35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE35" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="AF35" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:32">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2">
-        <v>45905</v>
+        <v>45902</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H36">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I36">
-        <v>5.2</v>
+        <v>4.19</v>
       </c>
       <c r="J36">
-        <v>8.63</v>
+        <v>8.33</v>
       </c>
       <c r="K36">
         <v>34</v>
       </c>
       <c r="L36">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="M36">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="N36">
-        <v>3296.5</v>
+        <v>3546.4</v>
       </c>
       <c r="O36">
-        <v>3296.5</v>
+        <v>3546.4</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36" s="2">
+        <v>45912</v>
+      </c>
+      <c r="R36" t="s">
+        <v>79</v>
+      </c>
+      <c r="S36" t="s">
+        <v>80</v>
+      </c>
+      <c r="T36" s="2">
+        <v>45902</v>
+      </c>
+      <c r="U36" s="2">
         <v>45907</v>
       </c>
-      <c r="R36" t="s">
-        <v>54</v>
-      </c>
-      <c r="S36" t="s">
-        <v>55</v>
-      </c>
-      <c r="T36" s="2">
-        <v>45905</v>
-      </c>
-      <c r="U36" s="2">
-        <v>45910</v>
-      </c>
       <c r="V36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W36">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="X36" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="Y36" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="Z36" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AA36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB36" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="AC36" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="AD36">
+        <v>290631</v>
       </c>
       <c r="AE36" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="AF36" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:32">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" s="2">
-        <v>45906</v>
+        <v>45902</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H37">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="I37">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="J37">
-        <v>8.46</v>
+        <v>8.74</v>
       </c>
       <c r="K37">
         <v>34</v>
       </c>
       <c r="L37">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M37">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="N37">
-        <v>3760.5</v>
+        <v>2339.2</v>
       </c>
       <c r="O37">
-        <v>3706</v>
+        <v>2305.2</v>
       </c>
       <c r="P37">
         <v>0</v>
       </c>
       <c r="Q37" s="2">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="R37" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="S37" t="s">
+        <v>56</v>
+      </c>
+      <c r="T37" s="2">
+        <v>45902</v>
+      </c>
+      <c r="U37" s="2">
+        <v>45907</v>
+      </c>
+      <c r="V37" t="s">
         <v>41</v>
       </c>
-      <c r="T37" s="2">
-        <v>45906</v>
-      </c>
-      <c r="U37" s="2">
-        <v>45911</v>
-      </c>
-      <c r="V37" t="s">
-        <v>42</v>
-      </c>
       <c r="W37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X37" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="Y37" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AA37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB37" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="AC37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD37" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="AE37" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="AF37" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:33">
+    <row r="38" spans="1:32">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45901</v>
+      </c>
+      <c r="F38" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="2">
-        <v>45907</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H38">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I38">
-        <v>4.02</v>
+        <v>5.06</v>
       </c>
       <c r="J38">
-        <v>8.59</v>
+        <v>8.24</v>
       </c>
       <c r="K38">
         <v>34</v>
       </c>
       <c r="L38">
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="M38">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="N38">
-        <v>2278</v>
+        <v>2837.2</v>
       </c>
       <c r="O38">
-        <v>2244.5</v>
+        <v>2755.2</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38" s="2">
-        <v>45909</v>
+        <v>45912</v>
       </c>
       <c r="R38" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="S38" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="T38" s="2">
-        <v>45907</v>
+        <v>45901</v>
       </c>
       <c r="U38" s="2">
-        <v>45912</v>
+        <v>45906</v>
       </c>
       <c r="V38" t="s">
+        <v>41</v>
+      </c>
+      <c r="W38">
+        <v>4.3</v>
+      </c>
+      <c r="X38" t="s">
         <v>42</v>
       </c>
-      <c r="W38">
-        <v>4.7</v>
-      </c>
-      <c r="X38" t="s">
-        <v>112</v>
-      </c>
       <c r="Y38" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="Z38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AA38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB38" t="s">
         <v>46</v>
       </c>
-      <c r="AB38" t="s">
-        <v>115</v>
-      </c>
       <c r="AC38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD38" t="s">
         <v>48</v>
       </c>
-      <c r="AD38" t="s">
+      <c r="AE38" t="s">
         <v>49</v>
       </c>
-      <c r="AE38" t="s">
-        <v>116</v>
-      </c>
       <c r="AF38" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="39" spans="1:33">
-      <c r="A39" t="s">
-        <v>109</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
-      </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E39" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H39">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="I39">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="J39">
-        <v>8.06</v>
+        <v>8.7</v>
       </c>
       <c r="K39">
         <v>34</v>
       </c>
       <c r="L39">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M39">
-        <v>33.7</v>
+        <v>34.6</v>
       </c>
       <c r="N39">
-        <v>3967.2</v>
+        <v>3375.9</v>
       </c>
       <c r="O39">
-        <v>3909.2</v>
+        <v>3425.4</v>
       </c>
       <c r="P39">
         <v>0</v>
       </c>
       <c r="Q39" s="2">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="R39" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="T39" s="2">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="U39" s="2">
-        <v>45913</v>
+        <v>45906</v>
       </c>
       <c r="V39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W39">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="X39" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="Y39" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="Z39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AA39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB39" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="AC39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD39" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AE39" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="AF39" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:33">
+    <row r="40" spans="1:32">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45901</v>
+      </c>
+      <c r="F40" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="2">
-        <v>45909</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
       <c r="G40" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H40">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I40">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
       <c r="J40">
-        <v>8.61</v>
+        <v>8.39</v>
       </c>
       <c r="K40">
         <v>34</v>
       </c>
       <c r="L40">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="M40">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="N40">
-        <v>2463.7</v>
+        <v>2664.2</v>
       </c>
       <c r="O40">
-        <v>2499.2</v>
+        <v>2702.7</v>
       </c>
       <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40" s="2">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="R40" t="s">
+        <v>39</v>
+      </c>
+      <c r="S40" t="s">
         <v>40</v>
       </c>
-      <c r="S40" t="s">
+      <c r="T40" s="2">
+        <v>45901</v>
+      </c>
+      <c r="U40" s="2">
+        <v>45906</v>
+      </c>
+      <c r="V40" t="s">
         <v>41</v>
       </c>
-      <c r="T40" s="2">
-        <v>45909</v>
-      </c>
-      <c r="U40" s="2">
-        <v>45914</v>
-      </c>
-      <c r="V40" t="s">
-        <v>42</v>
-      </c>
       <c r="W40">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="X40" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="Y40" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="Z40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AA40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB40" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="AC40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="AD40" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AE40" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="AF40" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:32">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45901</v>
+      </c>
+      <c r="F41" t="s">
         <v>37</v>
       </c>
-      <c r="E41" s="2">
-        <v>45910</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H41">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="I41">
-        <v>3.85</v>
+        <v>4.99</v>
       </c>
       <c r="J41">
-        <v>8.52</v>
+        <v>8.12</v>
       </c>
       <c r="K41">
         <v>34</v>
       </c>
       <c r="L41">
-        <v>33.9</v>
+        <v>34.6</v>
       </c>
       <c r="M41">
-        <v>32.9</v>
+        <v>34.1</v>
       </c>
       <c r="N41">
-        <v>3288.3</v>
+        <v>3667.6</v>
       </c>
       <c r="O41">
-        <v>3191.3</v>
+        <v>3614.6</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -6751,56 +6620,56 @@
         <v>45912</v>
       </c>
       <c r="R41" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="S41" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="T41" s="2">
-        <v>45910</v>
+        <v>45901</v>
       </c>
       <c r="U41" s="2">
-        <v>45915</v>
+        <v>45906</v>
       </c>
       <c r="V41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W41">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="X41" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AA41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AB41" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="AC41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD41" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="AE41" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="AF41" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AH41" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AG41" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:AG41">
+      <sortCondition ref="Q1" descending="1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/farmer_milk_data.xlsx
+++ b/farmer_milk_data.xlsx
@@ -254,7 +254,7 @@
     <t>10092025F9014</t>
   </si>
   <si>
-    <t>Amit Shah</t>
+    <t>Ramanlal Bhai</t>
   </si>
   <si>
     <t>F9015</t>
@@ -6667,7 +6667,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AG41" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:AG41">
+    <sortState ref="A1:AG41">
       <sortCondition ref="Q1" descending="1"/>
     </sortState>
     <extLst/>
